--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/TEXAS_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/TEXAS_2022.xlsx
@@ -499,7 +499,7 @@
         <v>114</v>
       </c>
       <c r="D8">
-        <v>0.0009467101821171429</v>
+        <v>0.0009467101821171428</v>
       </c>
     </row>
     <row r="9">
@@ -571,7 +571,7 @@
         <v>12</v>
       </c>
       <c r="D12">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="13">
@@ -1057,7 +1057,7 @@
         <v>12</v>
       </c>
       <c r="D39">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="40">
@@ -1435,7 +1435,7 @@
         <v>12</v>
       </c>
       <c r="D60">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="61">
@@ -2641,7 +2641,7 @@
         <v>12</v>
       </c>
       <c r="D127">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="128">
@@ -3109,7 +3109,7 @@
         <v>12</v>
       </c>
       <c r="D153">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="154">
@@ -3649,7 +3649,7 @@
         <v>12</v>
       </c>
       <c r="D183">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="184">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C202">
@@ -4207,7 +4207,7 @@
         <v>12</v>
       </c>
       <c r="D214">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="215">
@@ -4261,7 +4261,7 @@
         <v>12</v>
       </c>
       <c r="D217">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="218">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C265">
@@ -5719,7 +5719,7 @@
         <v>12</v>
       </c>
       <c r="D298">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="299">
@@ -6529,7 +6529,7 @@
         <v>12</v>
       </c>
       <c r="D343">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="344">
@@ -7213,7 +7213,7 @@
         <v>12</v>
       </c>
       <c r="D381">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="382">
@@ -7267,7 +7267,7 @@
         <v>12</v>
       </c>
       <c r="D384">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="385">
@@ -7339,7 +7339,7 @@
         <v>12</v>
       </c>
       <c r="D388">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="389">
@@ -7789,7 +7789,7 @@
         <v>12</v>
       </c>
       <c r="D413">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="414">
@@ -7825,7 +7825,7 @@
         <v>117</v>
       </c>
       <c r="D415">
-        <v>0.0009716236079623309</v>
+        <v>0.0009716236079623308</v>
       </c>
     </row>
     <row r="416">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C417">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C427">
@@ -8347,7 +8347,7 @@
         <v>1171</v>
       </c>
       <c r="D444">
-        <v>0.009724540554905039</v>
+        <v>0.009724540554905041</v>
       </c>
     </row>
     <row r="445">
@@ -9319,7 +9319,7 @@
         <v>12</v>
       </c>
       <c r="D498">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="499">
@@ -9715,7 +9715,7 @@
         <v>109</v>
       </c>
       <c r="D520">
-        <v>0.0009051878057084963</v>
+        <v>0.0009051878057084965</v>
       </c>
     </row>
     <row r="521">
@@ -9913,7 +9913,7 @@
         <v>12</v>
       </c>
       <c r="D531">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="532">
@@ -10417,7 +10417,7 @@
         <v>12</v>
       </c>
       <c r="D559">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="560">
@@ -11281,7 +11281,7 @@
         <v>12</v>
       </c>
       <c r="D607">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="608">
@@ -12199,7 +12199,7 @@
         <v>1095</v>
       </c>
       <c r="D658">
-        <v>0.009093400433493611</v>
+        <v>0.009093400433493612</v>
       </c>
     </row>
     <row r="659">
@@ -13225,7 +13225,7 @@
         <v>12</v>
       </c>
       <c r="D715">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="716">
@@ -14359,7 +14359,7 @@
         <v>12</v>
       </c>
       <c r="D778">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="779">
@@ -14431,7 +14431,7 @@
         <v>12</v>
       </c>
       <c r="D782">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="783">
@@ -14809,7 +14809,7 @@
         <v>12</v>
       </c>
       <c r="D803">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="804">
@@ -14845,7 +14845,7 @@
         <v>12</v>
       </c>
       <c r="D805">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="806">
@@ -15169,7 +15169,7 @@
         <v>12</v>
       </c>
       <c r="D823">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="824">
@@ -15655,7 +15655,7 @@
         <v>12</v>
       </c>
       <c r="D850">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="851">
@@ -16195,7 +16195,7 @@
         <v>12</v>
       </c>
       <c r="D880">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="881">
@@ -16519,7 +16519,7 @@
         <v>12</v>
       </c>
       <c r="D898">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="899">
@@ -16890,14 +16890,14 @@
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C919">
         <v>12</v>
       </c>
       <c r="D919">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="920">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C921">
@@ -16944,7 +16944,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C922">
@@ -17311,7 +17311,7 @@
         <v>12</v>
       </c>
       <c r="D942">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="943">
@@ -18931,7 +18931,7 @@
         <v>12</v>
       </c>
       <c r="D1032">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1033">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1071">
@@ -19813,7 +19813,7 @@
         <v>12</v>
       </c>
       <c r="D1081">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1082">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1119">
@@ -20508,7 +20508,7 @@
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1120">
@@ -20616,7 +20616,7 @@
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1126">
@@ -21037,7 +21037,7 @@
         <v>12</v>
       </c>
       <c r="D1149">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1150">
@@ -21811,7 +21811,7 @@
         <v>12</v>
       </c>
       <c r="D1192">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1193">
@@ -22369,7 +22369,7 @@
         <v>12</v>
       </c>
       <c r="D1223">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1224">
@@ -22380,7 +22380,7 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1224">
@@ -24655,7 +24655,7 @@
         <v>12</v>
       </c>
       <c r="D1350">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1351">
@@ -24691,7 +24691,7 @@
         <v>12</v>
       </c>
       <c r="D1352">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1353">
@@ -25519,7 +25519,7 @@
         <v>12</v>
       </c>
       <c r="D1398">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1399">
@@ -27517,7 +27517,7 @@
         <v>12</v>
       </c>
       <c r="D1509">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1510">
@@ -27571,7 +27571,7 @@
         <v>12</v>
       </c>
       <c r="D1512">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1513">
@@ -28507,7 +28507,7 @@
         <v>12</v>
       </c>
       <c r="D1564">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1565">
@@ -28795,7 +28795,7 @@
         <v>12</v>
       </c>
       <c r="D1580">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1581">
@@ -28813,7 +28813,7 @@
         <v>12</v>
       </c>
       <c r="D1581">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1582">
@@ -29065,7 +29065,7 @@
         <v>117</v>
       </c>
       <c r="D1595">
-        <v>0.0009716236079623309</v>
+        <v>0.0009716236079623308</v>
       </c>
     </row>
     <row r="1596">
@@ -30505,7 +30505,7 @@
         <v>12</v>
       </c>
       <c r="D1675">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1676">
@@ -30516,7 +30516,7 @@
       </c>
       <c r="B1676" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1676">
@@ -30541,7 +30541,7 @@
         <v>12</v>
       </c>
       <c r="D1677">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1678">
@@ -30757,7 +30757,7 @@
         <v>12</v>
       </c>
       <c r="D1689">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1690">
@@ -30865,7 +30865,7 @@
         <v>12</v>
       </c>
       <c r="D1695">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1696">
@@ -31513,7 +31513,7 @@
         <v>12</v>
       </c>
       <c r="D1731">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1732">
@@ -32521,7 +32521,7 @@
         <v>12</v>
       </c>
       <c r="D1787">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1788">
@@ -32755,7 +32755,7 @@
         <v>12</v>
       </c>
       <c r="D1800">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1801">
@@ -34879,7 +34879,7 @@
         <v>110</v>
       </c>
       <c r="D1918">
-        <v>0.0009134922809902257</v>
+        <v>0.0009134922809902256</v>
       </c>
     </row>
     <row r="1919">
@@ -35347,7 +35347,7 @@
         <v>12</v>
       </c>
       <c r="D1944">
-        <v>9.965370338075189E-05</v>
+        <v>9.965370338075188E-05</v>
       </c>
     </row>
     <row r="1945">
